--- a/ecv/extraccion_ecv_2017/ecv_2017_wide.xlsx
+++ b/ecv/extraccion_ecv_2017/ecv_2017_wide.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:X12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -402,62 +402,77 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>dep_economica_total</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>IMCV_urbano</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>estrato_urbano</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>calidad_vivienda_urbano</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>num_servicios_pub_urbano</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>num_servicios_suspendidos_urbano</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>tasa_desempleo_urbano</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>dep_economica_urbano</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>IMCV_rural</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>estrato_rural</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>calidad_vivienda_rural</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>num_servicios_pub_rural</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>num_servicios_suspendidos_rural</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>tasa_desempleo_rural</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dep_economica_rural</t>
         </is>
       </c>
     </row>
@@ -494,16 +509,25 @@
         <v>15.1930050081607</v>
       </c>
       <c r="J2">
+        <v>49.5912806539509</v>
+      </c>
+      <c r="K2">
         <v>32.3679614775725</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>15.8747940970853</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
+        <v>47.4251497005988</v>
+      </c>
+      <c r="R2">
         <v>24.7700338028169</v>
       </c>
-      <c r="U2">
+      <c r="W2">
         <v>8.372888823758331</v>
+      </c>
+      <c r="X2">
+        <v>56.390977443609</v>
       </c>
     </row>
     <row r="3">
@@ -539,16 +563,25 @@
         <v>22.4005833713557</v>
       </c>
       <c r="J3">
+        <v>59.8119858989424</v>
+      </c>
+      <c r="K3">
         <v>28.6470733333335</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>31.3524206197161</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
+        <v>61.5755627009646</v>
+      </c>
+      <c r="R3">
         <v>24.1350123188405</v>
       </c>
-      <c r="U3">
+      <c r="W3">
         <v>12.8454758533176</v>
+      </c>
+      <c r="X3">
+        <v>55.0218340611353</v>
       </c>
     </row>
     <row r="4">
@@ -584,16 +617,25 @@
         <v>6.0296869511016</v>
       </c>
       <c r="J4">
+        <v>41.0515672396359</v>
+      </c>
+      <c r="K4">
         <v>32.8276140109887</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>5.75332520819535</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
+        <v>38.0758807588075</v>
+      </c>
+      <c r="R4">
         <v>26.2558354166666</v>
       </c>
-      <c r="U4">
+      <c r="W4">
         <v>6.89737114452791</v>
+      </c>
+      <c r="X4">
+        <v>49.800796812749</v>
       </c>
     </row>
     <row r="5">
@@ -629,16 +671,25 @@
         <v>9.68814326651451</v>
       </c>
       <c r="J5">
+        <v>46.9901168014375</v>
+      </c>
+      <c r="K5">
         <v>29.7488725333334</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>9.89451989498712</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
+        <v>44.5614035087719</v>
+      </c>
+      <c r="R5">
         <v>26.8761588235293</v>
       </c>
-      <c r="U5">
+      <c r="W5">
         <v>8.15189603699463</v>
+      </c>
+      <c r="X5">
+        <v>55.0387596899224</v>
       </c>
     </row>
     <row r="6">
@@ -674,16 +725,25 @@
         <v>1.02320028799206</v>
       </c>
       <c r="J6">
+        <v>35.9375</v>
+      </c>
+      <c r="K6">
         <v>24.5941416666666</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>4.79419251332418</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
+        <v>34.0782122905027</v>
+      </c>
+      <c r="R6">
         <v>21.9084904255319</v>
       </c>
-      <c r="U6">
+      <c r="W6">
         <v>0</v>
+      </c>
+      <c r="X6">
+        <v>38.2978723404255</v>
       </c>
     </row>
     <row r="7">
@@ -719,16 +779,25 @@
         <v>3.08560352169881</v>
       </c>
       <c r="J7">
+        <v>50.9461426491994</v>
+      </c>
+      <c r="K7">
         <v>30.2800240157481</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>3.5369308409673</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
+        <v>51.0775862068965</v>
+      </c>
+      <c r="R7">
         <v>24.6705906779661</v>
       </c>
-      <c r="U7">
+      <c r="W7">
         <v>2.6008293691199</v>
+      </c>
+      <c r="X7">
+        <v>50.6726457399103</v>
       </c>
     </row>
     <row r="8">
@@ -764,16 +833,25 @@
         <v>5.4914142625512</v>
       </c>
       <c r="J8">
+        <v>55.1507537688442</v>
+      </c>
+      <c r="K8">
         <v>30.7100433121017</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>11.8747667282179</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
+        <v>49.7237569060773</v>
+      </c>
+      <c r="R8">
         <v>24.1724643835616</v>
       </c>
-      <c r="U8">
+      <c r="W8">
         <v>3.06624515475683</v>
+      </c>
+      <c r="X8">
+        <v>66.798418972332</v>
       </c>
     </row>
     <row r="9">
@@ -809,16 +887,25 @@
         <v>1.42971770049065</v>
       </c>
       <c r="J9">
+        <v>60.5612998522895</v>
+      </c>
+      <c r="K9">
         <v>28.0971675276754</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>3.83804354933335</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
+        <v>57.6659038901601</v>
+      </c>
+      <c r="R9">
         <v>23.628895035461</v>
       </c>
-      <c r="U9">
+      <c r="W9">
         <v>0.2191030957326</v>
+      </c>
+      <c r="X9">
+        <v>65.8333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -854,16 +941,25 @@
         <v>3.69326126943102</v>
       </c>
       <c r="J10">
+        <v>53.9456662354463</v>
+      </c>
+      <c r="K10">
         <v>29.1732840390879</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>6.94260443216629</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
+        <v>58.7771203155818</v>
+      </c>
+      <c r="R10">
         <v>22.6522397260273</v>
       </c>
-      <c r="U10">
+      <c r="W10">
         <v>0</v>
+      </c>
+      <c r="X10">
+        <v>44.7368421052631</v>
       </c>
     </row>
     <row r="11">
@@ -899,16 +995,25 @@
         <v>18.2603035622945</v>
       </c>
       <c r="J11">
+        <v>48.4270734032411</v>
+      </c>
+      <c r="K11">
         <v>28.8322021333332</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>35.0091337742072</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
+        <v>53.7949400798934</v>
+      </c>
+      <c r="R11">
         <v>26.168406081081</v>
       </c>
-      <c r="U11">
+      <c r="W11">
         <v>3.12884174935169</v>
+      </c>
+      <c r="X11">
+        <v>34.8993288590604</v>
       </c>
     </row>
     <row r="12">
@@ -944,16 +1049,25 @@
         <v>3.37153858264477</v>
       </c>
       <c r="J12">
+        <v>44.5054945054945</v>
+      </c>
+      <c r="K12">
         <v>25.1696121212121</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>4.14151270059479</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
+        <v>46.7479674796748</v>
+      </c>
+      <c r="R12">
         <v>24.6490117647058</v>
       </c>
-      <c r="U12">
+      <c r="W12">
         <v>2.8634680461448</v>
+      </c>
+      <c r="X12">
+        <v>39.8305084745762</v>
       </c>
     </row>
   </sheetData>
